--- a/outputs/matriz_procesada.xlsx
+++ b/outputs/matriz_procesada.xlsx
@@ -40,7 +40,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +106,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -483,7 +495,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -496,45 +508,45 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>FACULTAD</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>CARRERA</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>DOCENTE</t>
         </is>
       </c>
-      <c r="F1" s="4" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Identificación</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Apellidos y nombres</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Puesto</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Título de 3er nivel </t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Título de 4to. Nivel </t>
         </is>
@@ -564,12 +576,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION INSTRUMENTISTA PEDAGOGO</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
         </is>
@@ -601,12 +613,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO MUSICA CONTEMPORANEA</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>MAESTRIA EN MUSICA INTERPRETACION INSTRUMENTAL</t>
         </is>
@@ -638,12 +650,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN COMUNICACION SOCIAL ESPECIALIZACION EN INVESTIGACION</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>DOCTOR/A EN HISTORIA LATINOAMERICANA | MAGISTER EN ESTUDIOS DE LA CULTURA MENCION LITERATURA HISPANOAMERICANA</t>
         </is>
@@ -675,12 +687,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION INSTRUMENTISTA PEDAGOGO EN PIANO | TECNOLOGO MUSICAL MENCION PIANO</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN PEDAGOGIA E INVESTIGACION MUSICAL | MASTER UNIVERSITARIO EN INTERPRETACION E INVESTIGACION MUSICAL EN LA ESPECIALIDAD EN INTERPRETACION MUSICAL</t>
         </is>
@@ -712,12 +724,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN ARTES ESPECIALIZACIONES PINTURA Y GRABADO</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
         </is>
@@ -749,12 +761,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>MASTER EN PIANO CONCERT PERFORMING ART</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>MASTER EN PIANO CONCERT PERFORMING ART</t>
         </is>
@@ -786,12 +798,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>LICENCIADA EN ARTES ESPECIALIZACIONES PINTURA Y CERAMICA</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ANTROPOLOGIA VISUAL Y DOCUMENTAL ANTROPOLOGICO</t>
         </is>
@@ -823,12 +835,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION PEDAGOGIA MUSICAL</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN EDUCACION INTERCULTURAL E INCLUSIVA</t>
         </is>
@@ -860,12 +872,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION Y PROFESOR DE SEGUNDA ENSEÑANZA EN ESPECIALIZACION DE FISICA Y MATEMATICA</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>DIPLOMA ARTISTICO EN DIRECCION DE ESCENA | MASTER UNIVERSITARIO EN ARTES DEL ESPECTACULO VIVO</t>
         </is>
@@ -897,12 +909,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>INGENIERO DE SONIDO Y ACUSTICA</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>MASTER OF SCIENCE IN SOUND DESIGN</t>
         </is>
@@ -934,12 +946,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN ARTES CON MENCION EN DANZA</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
         </is>
@@ -971,12 +983,12 @@
           <t xml:space="preserve">AUXILIAR 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>DISEÑADORA MENCION GRAFICO INDUSTRIAL | LICENCIADA EN CIENCIAS DE LA COMUNICACION</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>ESPECIALISTA EN LOGICA Y TECNICA DE LA FORMA | MAGISTER EN LOGICA Y TECNICA DE LA FORMA</t>
         </is>
@@ -1008,12 +1020,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN SOCIOLOGIA CON MENCION EN CIENCIA POLITICA</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
         </is>
@@ -1045,12 +1057,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA CERAMICA</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN GESTION CULTURAL | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
         </is>
@@ -1082,14 +1094,4047 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>BACHELOR OF MUSIC</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>MASTER OF ARTS FIELD ETHNOMUSICOLOGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0801681297</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>AYOVI QUIÑONEZ JAKSON SANDRO</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION INTERCULTURAL E INCLUSIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1713099016</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>BAQUERO PAEZ JOSE JAVIER</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO MUSICA CONTEMPORANEA</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1709336935</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>BARREIRO LUDENA PEDRO FERNANDO</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1716107360</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>BELDUMA CUENCA BENITO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION ESPECIALIDAD INSTRUMENTISTA PEDAGOGO EN GUITARRA | TECNOLOGO EN MUSICA MENCION GUITARRA | PROFESOR DE SEGUNDA ENSEÑANZA. ESPECIALIDAD PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>MASTER EN ENSEÑANZAS ARTISTICAS EN COMPOSICION APLICADA A LOS MEDIOS AUDIOVISUALES Y ESCENICOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1707773196</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>BETANCOURT CAMPOS OSCAR SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN GESTION PARA EL DESARROLLO LOCAL SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN GESTION CULTURAL Y POLITICAS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1722941414</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>BORJA BERMEO ANA LIA</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN COMUNICACION CON MENCION EN PERIODISMO PARA PRENSA RADIO Y TELEVISION</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN TEATRO Y ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1713005864</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>BORJA CERDA DIANA SERENE</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES ESPECIALIDAD ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>DIPLOMA SUPERIOR EN ARTES ESCENICAS | MAESTRIA EN DRAMATURGIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1712176294</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BRACERO TORRES ANDRES PATRICIO</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO PRODUCCION MUSICAL Y SONIDO</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1715790141</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>BRITO ACOSTA DANIEL EUDORO</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30.75" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0603129867</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>BRITO LOBATO SILVIA VERÓNICA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>INGENIERO EN SISTEMAS</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>1711750818</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CACERES CARRASCO LUIS AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1710522341</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CALLE BARRETO ROBERTO JACINTO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIDAD PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1725020372</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CELI RAMOS MATEO ADRIANO</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>DIPLOMA SUPERIOR DE ENSEÑANZA ESPECIALIZACION VIOLONCHELO</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>DIPLOMA SUPERIOR DE ENSEÑANZA ESPECIALIZACION VIOLONCHELO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>1711739936</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>CLAVIJO AGUIRRE KARINA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION ESPECIALIDAD INSTRUMENTISTA PEDAGOGO EN CANTO | PROFESORA DE SEGUNDA ENSEÑANZA. ESPECIALIDAD PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA | ESPECIALISTA EN GERENCIA EDUCATIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>1716270325</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>COBAGANGO CASTILLO ANA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES MENCION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1710885573</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>CORAL  LOPEZ DIEGO GABRIEL</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CINE Y AUDIOVISUALES | TECNOLOGO EN REALIZACION CINEMATOGRAFICA MENCION DIRECCION Y DRAMATURGIA</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN CREACION DE GUIONES AUDIOVISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>1710815208</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CORDOVA RAMIREZ FRANCINE OSWALDO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA VISUAL | MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1716386758</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>CORTEZ GUAMBA EDGAR WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>COMUNICADOR SOCIAL CON ENFASIS EN EDUCOMUNICACION, ARTE Y CULTURA</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>MAGÍSTER EN COMUNICACIÓN AUDIOVISUAL  MENCIÓN EN INVESTIGACIÓN DE MEDIOS Y DOCENCIA EN COMUNICACIÓN | MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>1104730716</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CUEVA YAGUANA PEPE KAICER</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN COMUNICACION SOCIAL | TECNOLOGO EN ACTUACION PARA TELEVISION MENCION DIRECCION ESCENICA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN ARTES DEL ESPECTACULO VIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>1304612011</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ENRIQUEZ CEVALLOS KATTERINE MIRELLA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALISTA EN DISEÑO DE POLITICAS PUBLICAS | MAGISTER EN GESTION CULTURAL Y POLITICAS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>1711997179</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ESCUDERO ARCINIEGAS JAVIER OMAR</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES, ESPECIALIZACIONES PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>0102287067</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>FALCONI ABAD FERNANDO EDUARDO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN ARTE Y NUEVAS TECNOLOGIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>1722660246</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>FRANCO VAREA MARTINA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN CIENCIAS HUMANAS Y SOCIALES MENCION PSICOLOGIA</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN PSICOLOGIA CLINICA Y DE LA SALUD ESPECIALIZACION EN PSICOLOGIA  DE LA SALUD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>1715023667</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>GALLEGOS ROMERO ROMULO FABIAN</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION ESP. INSTRUMENTISTA PEDAGOGO EN TROMBON | PROFESOR DE SEGUNDA ENSEÑANZA ESPEC. PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA E INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>1725457053</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>GALVÁN VALAREZO EDISON ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>1720851367</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA ALVARADO TIANI SAMAY</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>1709780769</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA COQUE JHONY EFREN</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>1001992773</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA MORENO MARIO FERNANDO</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES EN LAS ESPECIALIDADES DE ESCULTURA Y CERAMICA</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE | DOCTOR DENTRO DEL PROGRAMA DE DOCTORADO EN ARTE: PRODUCCION E INVESTIGACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>1712211059</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA PAEZ  JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF SCIENCE IN ENVIRONMENTAL STUDIES</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN TEORIA Y PRACTICA DEL DOCUMENTAL CREATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>1726263179</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>GARZON PEÑAFIEL KARLA PRISCILA</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LITERATURA MENCIÓN EN LITERATURA INFANTIL Y JUVENIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>1708556467</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>GODOY MUÑOZ FREDDY VICENTE</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION ESPECIALIDAD INSTRUMENTISTA PEDAGOGO EN CANTO</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA E INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>1757270077</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>GONZALEZ CISNEROS CESAR ALBERTO</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN EDUCACION BASICA INTEGRAL</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN MUSICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>1707217889</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>GUANOLUISA CEDILLO FRANKLIN PATRICIO</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA - GRABADO</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>1706526884</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA CARRERA NATALIA SALOME</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC THERAPY</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>1707376016</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>GUERRERO GUTIERREZ FIDEL PABLO</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>1002065801</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>GUZMAN TORO CESAR ERNESTO</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>MUSICO - PIANISTA</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>1722826524</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>HINOJOSA OÑA EDUARDO JAVIER</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>1802990026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>JARA COBO DAVID EDUARDO</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES PLASTICAS</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA VISUAL Y DOCUMENTAL ANTROPOLOGICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>1711973741</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>JARAMILLO LOPEZ DAVID ANDRES</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>HISTORIADOR DEL ARTE | LICENCIADO EN ARTES MENCION ESCULTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION ARTES Y ESTUDIOS VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>1711890556</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>LEON BORJA XAVIER ESTEBAN</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>BACCALAUREUS ARTIUM - LICENCIADO - FINANZAS - ECONOMIA</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTADISTICA APLICADA, MSC. | MAESTRO EN ARTES VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>1721200796</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>LIMA GUAMAN ROCIO ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC IN FLUTE PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALISTA EN PROYECTOS DE DESARROLLO Y LEVANTAMIENTO DE FONDOS | MASTER OF MUSIC CONCENTRATION: PERFORMANCE AND LITERATURE | DOCTOR OF MUSICAL ARTS IN PERFORMANCE AND LITERATURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>1706896535</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>LOAYZA CABEZAS GRIMANESA MADELEINE</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ACTUACION</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ARTES ESCENICAS | DOCTORA DENTRO DEL PROGRAMA DE DOCTORADO EN ARTE: PRODUCCION E INVESTIGACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>1711587046</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>LUZURIAGA GUARICELA NATALIA ISABEL</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO SICOLOGIA</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>1760954964</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>MATEUS VALBUENA HERACLIO ARMANDO</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>MUSICO TROMPETISTA CON ENFASIS EN DIRECCION</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN ENSEÑANZAS ARTISTICAS DE ESTUDIOS AVANZADOS EN INTERPRETACION: INSTRUMENTOS DE LA MUSICA CLASICA Y CONTEMPORANEA-TROMPETA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>1724687171</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>MICHELENA ORDOÑEZ  CARLA IVANNIA</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF ARTS IN CONTEMPORARY PERFORMANCE PRACTICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>1711659100</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>MORAL SOSA SOFIA AMARANTA</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN DISEÑO DE ESPECTACULOS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA VISUAL Y DOCUMENTAL ANTROPOLOGICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customFormat="1" customHeight="1" s="6">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>1003701974</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>MORAN CABASCANGO TAMYA SISA</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>LICENCIADA MUSICA CONTEMPORANEA | TECNOLOGO EN DOCENCIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION INTERCULTURAL E INCLUSIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>0801572702</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>MOSQUERA  JARAMILLO ROSA ELENA</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION MENCION PSICOLOGIA EDUCATIVA Y ORIENTACION</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION SUPERIOR Y EQUIDAD DE GENERO | ESPECIALISTA EN DISEÑO Y GESTION DE PROYECTOS EDUCATIVOS Y SOCIALES CON ENFOQUE DE GENERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>0104532858</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>NAULA CHACA JUAN PABLO</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS | MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>1715952246</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>NEGRETE SALAZAR PABLO MARTIN</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>1707622112</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>NORIEGA FERNANDEZ RAMIRO FABRICIO</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>LICENCE DE LITTERATURE GENERALE ET COMPAREE</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>DOCTEUR EN LITTERATURE GENERALE ET COMPAREE | DIPLOME D`ETUDES APPROFONDIES LITTERATURE GENERALE ET COMPAREE MENTION TRES BIEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>1721744041</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>NUÑEZ BAYAS MARIA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION MENCION PROFESORA PARVULARIA | TECNOLOGO/A SUPERIOR EN ACTUACION Y DIRECCION ESCENICA</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA EN LAS ARTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>1719319665</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>NUÑEZ  MORETA MARIA JOSE</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION MENCION MUSICA LENGUAJE Y MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN GESTION Y EMPRENDIMIENTO DE PROYECTOS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>1716116023</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>OLEAS RUEDA MARIA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>SOCIOLOGA CON MENCION EN DESARROLLO</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>DOCTOR/A EN HISTORIA DE LOS ANDES | MAGISTER EN ESTUDIOS DE LA CULTURA MENCION ARTES Y ESTUDIOS VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>1002940599</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>OÑA FONSECA FRANCISCO JAVIER</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CINE Y AUDIOVISUALES | TECNOLOGO EN REALIZACION Y ACTUACION DE CINE</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DIRECCION Y DRAMATURGIAS CONTEMPORANEAS | MASTER UNIVERSITARIO EN DIRECCION DE MARKETING INTERNACIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>0915800478</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>ORTEGA HUERTA FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>ABOGADO DE LOS TRIBUNALES Y JUZGADOS DE LA REPUBLICA | BACHELOR OF MUSIC</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>1711603850</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>PALYS REYES ANA MARIA</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>PROFESORA DE EDUCACION MEDIA EN LA ESPECIALIDAD DE LENGUA Y LITERATURA | LICENCIADA EN CIENCIAS DE LA EDUCACION EN LA ESPECIALIDAD DE LENGUA Y LITERATURA</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION ARTES Y ESTUDIOS VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>0502464282</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>PANCHI CULQUI JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION EDUCACION MUSICAL</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC, CONTRABASS | MASTER OF MUSIC, MUSIC EDUCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>1003588488</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>PEÑAFIEL SOLANO CAMPO ELIAS</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS | TECNOLOGO EN MUSICA MENCION PIANO</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA MENCIÓN EN MUSICA Y DIRECCION CORAL | MAGISTER EN PEDAGOGIA MENCIÓN EN EDUCACION TECNICA Y TECNOLOGICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>1710294891</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>PEREZ ESCALANTE MYRIAN GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA CERAMICA</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>1710563220</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>PEREZ CONSUELO DEL ROCIO</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION PROFESORA DE ENSEÑANZA MEDIA EN LA ESPECIALIZACION DE CASTELLANO Y LITERATURA</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DOCENCIA UNIVERSITARIA Y ADMINISTRACION EDUCATIVA | ESPECIALISTA EN DISEÑO CURRICULAR POR COMPETENCIAS | DOCTORA DENTRO DEL PROGRAMA DE DOCTORADO EN LENGUAS Y CULTURAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>0704360858</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>PESANTEZ CABRERA CARLOS BENITO</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>SOCIOLOGO</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN COMUNICACION CON MENCION EN OPINION PUBLICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>0801381294</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>PLAZA RODRIGUEZ GARY GASPAR</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>1709436123</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>PORTILLA KAROLIS CESAR AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>DOCTOR EN ESTETICA, CIENCIAS Y TECNOLOGIAS DE LAS ARTES - ESPECIALIDAD ARTES PLASTICAS Y FOTOGRAFIA | MASTER D´ARTS, MENTION ARTS PLASTIQUES, SPECIALITE THEORIE ET PRATIQUE DE L´ART CONTEMPORAIN E DES NOUVEAUX MEDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>1002015210</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>POZO RUIZ CARLOS EMILIO</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA GRABADO | TECNICO SUPERIOR EN ARTE GRAFICO</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>1713807020</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>PUEBLA CARDENAS OMAR DAVID</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES EN LAS ESPECIALIDADES DE ESCULTURA Y CERAMICA</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>1709162612</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>REVELO CARVAJAL CARLOS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>0151424520</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>RIOS LOPEZ JESUS</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>TITULO SUPERIOR DE MUSICA EN LA ESPECIALIDAD DE PIANO</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN FORMACION DEL PROFESORADO DE EDUCACION SECUNDARIA OBLIGATORIA Y BACHILLERATO, FORMACION PROFESIONAL Y ENSEÑANZA DE IDIOMAS EN LA ESPECIALIDAD EN MUSICA | MASTER ARTISTICO EN INTERPRETACION MUSICAL ESPECIALIDAD EN PIANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>1761226073</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>RIVERA CAMARGO GLORIA ESTEFANIA</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>MAESTRA EN MUSICA CON ENFASIS EN INTERPRETACION VIOLIN</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN ENSEÑANZAS ARTISTICAS EN INTERPRETACION DE MUSICA DE CAMARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>1758693855</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>RIVERO HERNANDEZ GILBERTO</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>1709635591</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PAZMINO LUIS DIMITROV</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN MUSICA | LICENCIADO EN MUSICA PERFIL COMPOSICION</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>1706950266</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PAZMIÑO ELENA PASIONARIA</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN HISTORIA DEL ARTE</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>LAUREA SPECIALISTICA IN STORIA DELL´ARTE MEDIEVALE, MODERNA E CONTEMPORANEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>1708241078</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ SANTAMARIA JUAN JOSE</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN COMUNICACION SOCIAL</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LITERATURA | MAGISTER EN ESTUDIOS DE LA CULTURA MENCION LITERATURA HISPANOAMERICANA | ESPECIALISTA SUPERIOR EN COMUNICACION MENCION COMUNICACION PARA LA EMPRESA | DOCTOR OF PHILOSOPHY IN LANGUAGES, CULTURES AND SOCIETIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>1710315993</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ  MERA SANTIAGO EDUARDO</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ACTUACION</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>1711577070</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ROMERO NARVAEZ WILMER PATRICIO</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>1720761020</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>ROSERO MARIÑO NADIA CONSTANTINA</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>BACCALAUREUS ARTIUM LICENCIADO EN DISEÑO GRAFICO</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DRAMATURGIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>1711110930</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>ROSERO MOSCOSO MARIA SOL</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN GESTION PARA EL DESARROLLO LOCAL SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>MASTER ARTES MENCION DANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>1719568303</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>RUIZ ANDRADE TAMIA MANAI</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF ARTS WITH A MAJOR IN THEATRE ARTS-DANCE</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF FINE ARTS IN DANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>1722501184</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>SALAS POLO BERNARDA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL | MASTER UNIVERSITARIO EN GESTION CULTURAL Y DE INDUSTRIAS CREATIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>1710285261</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ ARCOS VIVIANA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN GESTION PARA EL DESARROLLO LOCAL SOSTENIBLE | TECNOLOGO EN TERAPIAS NATURALES</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>1721238846</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ AUZ NATALY IVETH</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN ARTES MUSICALES CON ORIENTACION EN DIRECCION ORQUESTAL</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>1716214315</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ BENAVIDES MAYRA DANIELA</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>DISEÑADORA CON MENCION EN DISEÑO DE PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF ARTS, PERFORMANCE DESIGN AND PRACTICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>1715543979</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ ESPINOZA GILDA PAOLA</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN COMUNICACION SOCIAL | LICENCIADA EN ARTES, ESPECIALIZACION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA | MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>1714399100</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>SANTACRUZ VEGA LENNYN ARMANDO</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES MENCION ESCULTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>1714724349</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>SANTANDER GUERRERO GABRIELA GLORIA</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES VISUALES</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LENGUAJES ARTISTICOS COMBINADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>1717124125</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS ARIAS CARLA MARIELA</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>BACHARELADO EM MUSICA COM HABILITACAO EM INSTRUMENTO</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>1710211465</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS AVILES NELSON ANIBAL</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE | DOCTOR DENTRO DEL PROGRAMA DE DOCTORADO EN ARTE: PRODUCCION E INVESTIGACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>0601901093</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS TEJADA CÉSAR AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSIATRIO EN EDUCACION UNIVERSITARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>1715745590</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>SOLORZANO  SANCHEZ CRISTINA ROCIO</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>PSICOLOGA</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>MAGÍSTER EN INNOVACIÓN DE LA EDUCACIÓN | ESPECIALISTA EN GESTION DE LA CALIDAD EN EDUCACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>1710438589</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>SUBIA VALDEZ JOSE RAFAEL</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN COMPOSICION CON MEDIOS ELECTROACUSTICOS</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF SCIENCE IN DIGITAL COMPOSITION AND PERFORMANCE | DOCTOR OF PHILOSOPHY IN MUSICAL COMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>1711742211</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>TAPIA CRUZ JHOFFRE WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES MENCION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DIRECCION Y DRAMATURGIAS CONTEMPORANEAS | MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>1755904800</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>TARAZONA VENTO BEATRIZ</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>0603584350</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>TAYUPANDA ASHQUI CESAR BENITO</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION INSTRUMENTISTA PEDAGOGO EN CLARINETE</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN MUSICOLOGIA | MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>1713241279</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>TERAN ESPINOSA MARIA ENRIQUETA</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN DANZA</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN DOCENCIA UNIVERSITARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>1709984262</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>TITUAÑA LEMA MARTIN SAMUEL</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES MENCION ESCULTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION POLITICAS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>1711257483</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>TORAL ZAVALA OMAR ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>PROFESOR DE MUSICA INSTRUMENTO PRINCIPAL GUITARRA</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN INTERPRETACION DE MUSICA LATINOAMERICANA DEL SIGLO XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>1712205325</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>TORRES GANGULA ANDRES SANTIAGO</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>TEACHER´S TRAINING SPECIALIZATION PIANO</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>TEACHER´S TRAINING SPECIALIZATION PIANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>0601809155</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>UNDA LARA SANTIAGO ULISES</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION COMUNICACION | DOCTOR OF PHILOSOPHY IN VISUAL ARTS | MASTER OF FINE ARTS IN ELECTRONIC INTEGRATED ARTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>1757190648</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>URIBE SOTO RAFAEL ALONSO</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>INGENIERO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>DOCTOR EN CIENCIAS (QUIMICAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>1714158142</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>VACA TAMAYO EDISON ALVENIZ</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACIONES PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>1710020130</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>VALENCIA HINESTROSA JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>1707593594</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>VALLEJO ARISTIZABAL JOSE PATRICIO</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN SOCIOLOGIA Y CIENCIAS POLITICAS</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LETRAS MENCION ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>1712170222</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>VARGAS VILLALBA MARIO FIDEL</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO MUSICA CONTEMPORANEA</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1712193620</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>VELA MOSQUERA ANDREA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC IN PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN LA ESPECIALIDAD DE DIRECCION DE ORQUESTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>1705863049</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>VERDESOTO JACOME IRINA MARIBEL</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES MENCION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN CIENCIAS SOCIALES CON MENCION EN ANTROPOLOGIA | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>1712410172</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>VILLACIS GUERRERO OMAR STALIN</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>1715000608</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>VITERI  CHAVEZ CHRISTIAN PATRICIO</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACIONES PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>1715706238</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>ZALDUMBIDE MANOSALVAS JORGE LUIS</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>INGENIERO EN DISEÑO GRAFICO EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN LENGUAJES ARTISTICOS COMBINADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>0201860731</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>ZAPATA ESQUIVEL ALEXIS DAVID</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN MUSICA</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN INNOVACION EN EDUCACION | MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS</t>
         </is>
       </c>
     </row>

--- a/outputs/matriz_procesada.xlsx
+++ b/outputs/matriz_procesada.xlsx
@@ -40,7 +40,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +106,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -483,7 +495,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -496,45 +508,45 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>FACULTAD</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>CARRERA</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>DOCENTE</t>
         </is>
       </c>
-      <c r="F1" s="4" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Identificación</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Apellidos y nombres</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Puesto</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Título de 3er nivel </t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Título de 4to. Nivel </t>
         </is>
@@ -564,12 +576,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION INSTRUMENTISTA PEDAGOGO</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
         </is>
@@ -601,12 +613,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO MUSICA CONTEMPORANEA</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>MAESTRIA EN MUSICA INTERPRETACION INSTRUMENTAL</t>
         </is>
@@ -638,12 +650,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN COMUNICACION SOCIAL ESPECIALIZACION EN INVESTIGACION</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>DOCTOR/A EN HISTORIA LATINOAMERICANA | MAGISTER EN ESTUDIOS DE LA CULTURA MENCION LITERATURA HISPANOAMERICANA</t>
         </is>
@@ -675,12 +687,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION INSTRUMENTISTA PEDAGOGO EN PIANO | TECNOLOGO MUSICAL MENCION PIANO</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN PEDAGOGIA E INVESTIGACION MUSICAL | MASTER UNIVERSITARIO EN INTERPRETACION E INVESTIGACION MUSICAL EN LA ESPECIALIDAD EN INTERPRETACION MUSICAL</t>
         </is>
@@ -712,12 +724,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN ARTES ESPECIALIZACIONES PINTURA Y GRABADO</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
         </is>
@@ -749,12 +761,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>No registra</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>MASTER EN PIANO CONCERT PERFORMING ART</t>
         </is>
@@ -786,12 +798,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>LICENCIADA EN ARTES ESPECIALIZACIONES PINTURA Y CERAMICA</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ANTROPOLOGIA VISUAL Y DOCUMENTAL ANTROPOLOGICO</t>
         </is>
@@ -823,12 +835,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION PEDAGOGIA MUSICAL</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN EDUCACION INTERCULTURAL E INCLUSIVA</t>
         </is>
@@ -860,12 +872,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN CIENCIAS DE LA EDUCACION Y PROFESOR DE SEGUNDA ENSEÑANZA EN ESPECIALIZACION DE FISICA Y MATEMATICA</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>DIPLOMA ARTISTICO EN DIRECCION DE ESCENA | MASTER UNIVERSITARIO EN ARTES DEL ESPECTACULO VIVO</t>
         </is>
@@ -897,12 +909,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>INGENIERO DE SONIDO Y ACUSTICA</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>MASTER OF SCIENCE IN SOUND DESIGN</t>
         </is>
@@ -934,12 +946,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN ARTES CON MENCION EN DANZA</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
         </is>
@@ -971,12 +983,12 @@
           <t xml:space="preserve">AUXILIAR 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>DISEÑADORA MENCION GRAFICO INDUSTRIAL | LICENCIADA EN CIENCIAS DE LA COMUNICACION</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>ESPECIALISTA EN LOGICA Y TECNICA DE LA FORMA | MAGISTER EN LOGICA Y TECNICA DE LA FORMA</t>
         </is>
@@ -1008,12 +1020,12 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN SOCIOLOGIA CON MENCION EN CIENCIA POLITICA</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
         </is>
@@ -1045,12 +1057,12 @@
           <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA CERAMICA</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN GESTION CULTURAL | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
         </is>
@@ -1082,14 +1094,4047 @@
           <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>BACHELOR OF MUSIC</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>MASTER OF ARTS FIELD ETHNOMUSICOLOGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0801681297</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>AYOVI QUIÑONEZ JAKSON SANDRO</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION INTERCULTURAL E INCLUSIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1713099016</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>BAQUERO PAEZ JOSE JAVIER</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1709336935</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>BARREIRO LUDENA PEDRO FERNANDO</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1716107360</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>BELDUMA CUENCA BENITO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION ESPECIALIDAD INSTRUMENTISTA PEDAGOGO EN GUITARRA | TECNOLOGO EN MUSICA MENCION GUITARRA | PROFESOR DE SEGUNDA ENSEÑANZA. ESPECIALIDAD PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>MASTER EN ENSEÑANZAS ARTISTICAS EN COMPOSICION APLICADA A LOS MEDIOS AUDIOVISUALES Y ESCENICOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1707773196</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>BETANCOURT CAMPOS OSCAR SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN GESTION PARA EL DESARROLLO LOCAL SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN GESTION CULTURAL Y POLITICAS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1722941414</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>BORJA BERMEO ANA LIA</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN COMUNICACION CON MENCION EN PERIODISMO PARA PRENSA RADIO Y TELEVISION</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN TEATRO Y ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1713005864</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>BORJA CERDA DIANA SERENE</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES ESPECIALIDAD ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>DIPLOMA SUPERIOR EN ARTES ESCENICAS | MAESTRIA EN DRAMATURGIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1712176294</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BRACERO TORRES ANDRES PATRICIO</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO PRODUCCION MUSICAL Y SONIDO</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1715790141</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>BRITO ACOSTA DANIEL EUDORO</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30.75" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0603129867</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>BRITO LOBATO SILVIA VERÓNICA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>INGENIERO EN SISTEMAS</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>1711750818</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CACERES CARRASCO LUIS AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1710522341</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CALLE BARRETO ROBERTO JACINTO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIDAD PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1725020372</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CELI RAMOS MATEO ADRIANO</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>DIPLOMA SUPERIOR DE ENSEÑANZA ESPECIALIZACION VIOLONCHELO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>1711739936</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>CLAVIJO AGUIRRE KARINA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION ESPECIALIDAD INSTRUMENTISTA PEDAGOGO EN CANTO | PROFESORA DE SEGUNDA ENSEÑANZA. ESPECIALIDAD PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA | ESPECIALISTA EN GERENCIA EDUCATIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>1716270325</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>COBAGANGO CASTILLO ANA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES MENCION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1710885573</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>CORAL  LOPEZ DIEGO GABRIEL</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CINE Y AUDIOVISUALES | TECNOLOGO EN REALIZACION CINEMATOGRAFICA MENCION DIRECCION Y DRAMATURGIA</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN CREACION DE GUIONES AUDIOVISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>1710815208</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CORDOVA RAMIREZ FRANCINE OSWALDO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA VISUAL | MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1716386758</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>CORTEZ GUAMBA EDGAR WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>COMUNICADOR SOCIAL CON ENFASIS EN EDUCOMUNICACION, ARTE Y CULTURA</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>MAGÍSTER EN COMUNICACIÓN AUDIOVISUAL  MENCIÓN EN INVESTIGACIÓN DE MEDIOS Y DOCENCIA EN COMUNICACIÓN | MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>1104730716</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CUEVA YAGUANA PEPE KAICER</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN COMUNICACION SOCIAL | TECNOLOGO EN ACTUACION PARA TELEVISION MENCION DIRECCION ESCENICA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN ARTES DEL ESPECTACULO VIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>1304612011</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ENRIQUEZ CEVALLOS KATTERINE MIRELLA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALISTA EN DISEÑO DE POLITICAS PUBLICAS | MAGISTER EN GESTION CULTURAL Y POLITICAS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>1711997179</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ESCUDERO ARCINIEGAS JAVIER OMAR</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES, ESPECIALIZACIONES PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>0102287067</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>FALCONI ABAD FERNANDO EDUARDO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN ARTE Y NUEVAS TECNOLOGIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>1722660246</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>FRANCO VAREA MARTINA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN CIENCIAS HUMANAS Y SOCIALES MENCION PSICOLOGIA</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN PSICOLOGIA CLINICA Y DE LA SALUD ESPECIALIZACION EN PSICOLOGIA  DE LA SALUD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>1715023667</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>GALLEGOS ROMERO ROMULO FABIAN</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION ESP. INSTRUMENTISTA PEDAGOGO EN TROMBON | PROFESOR DE SEGUNDA ENSEÑANZA ESPEC. PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA E INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>1725457053</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>GALVÁN VALAREZO EDISON ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>1720851367</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA ALVARADO TIANI SAMAY</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>1709780769</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA COQUE JHONY EFREN</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>1001992773</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA MORENO MARIO FERNANDO</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES EN LAS ESPECIALIDADES DE ESCULTURA Y CERAMICA</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE | DOCTOR DENTRO DEL PROGRAMA DE DOCTORADO EN ARTE: PRODUCCION E INVESTIGACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>1712211059</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>GARCIA PAEZ  JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF SCIENCE IN ENVIRONMENTAL STUDIES</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN TEORIA Y PRACTICA DEL DOCUMENTAL CREATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>1726263179</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>GARZON PEÑAFIEL KARLA PRISCILA</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LITERATURA MENCIÓN EN LITERATURA INFANTIL Y JUVENIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>1708556467</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>GODOY MUÑOZ FREDDY VICENTE</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION ESPECIALIDAD INSTRUMENTISTA PEDAGOGO EN CANTO</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA E INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>1757270077</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>GONZALEZ CISNEROS CESAR ALBERTO</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN EDUCACION BASICA INTEGRAL</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN MUSICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>1707217889</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>GUANOLUISA CEDILLO FRANKLIN PATRICIO</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA - GRABADO</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>1706526884</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA CARRERA NATALIA SALOME</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC THERAPY</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>1707376016</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>GUERRERO GUTIERREZ FIDEL PABLO</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>1002065801</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>GUZMAN TORO CESAR ERNESTO</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>MUSICO - PIANISTA</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>1722826524</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>HINOJOSA OÑA EDUARDO JAVIER</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>1802990026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>JARA COBO DAVID EDUARDO</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES PLASTICAS</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA VISUAL Y DOCUMENTAL ANTROPOLOGICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>1711973741</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>JARAMILLO LOPEZ DAVID ANDRES</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>HISTORIADOR DEL ARTE | LICENCIADO EN ARTES MENCION ESCULTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION ARTES Y ESTUDIOS VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>1711890556</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>LEON BORJA XAVIER ESTEBAN</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>BACCALAUREUS ARTIUM - LICENCIADO - FINANZAS - ECONOMIA</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTADISTICA APLICADA, MSC. | MAESTRO EN ARTES VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>1721200796</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>LIMA GUAMAN ROCIO ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC IN FLUTE PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>ESPECIALISTA EN PROYECTOS DE DESARROLLO Y LEVANTAMIENTO DE FONDOS | MASTER OF MUSIC CONCENTRATION: PERFORMANCE AND LITERATURE | DOCTOR OF MUSICAL ARTS IN PERFORMANCE AND LITERATURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>1706896535</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>LOAYZA CABEZAS GRIMANESA MADELEINE</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ACTUACION</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ARTES ESCENICAS | DOCTORA DENTRO DEL PROGRAMA DE DOCTORADO EN ARTE: PRODUCCION E INVESTIGACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>1711587046</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>LUZURIAGA GUARICELA NATALIA ISABEL</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO SICOLOGIA</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>1760954964</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>MATEUS VALBUENA HERACLIO ARMANDO</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>MUSICO TROMPETISTA CON ENFASIS EN DIRECCION</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN ENSEÑANZAS ARTISTICAS DE ESTUDIOS AVANZADOS EN INTERPRETACION: INSTRUMENTOS DE LA MUSICA CLASICA Y CONTEMPORANEA-TROMPETA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>1724687171</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>MICHELENA ORDOÑEZ  CARLA IVANNIA</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF ARTS IN CONTEMPORARY PERFORMANCE PRACTICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>1711659100</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>MORAL SOSA SOFIA AMARANTA</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN DISEÑO DE ESPECTACULOS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA VISUAL Y DOCUMENTAL ANTROPOLOGICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customFormat="1" customHeight="1" s="6">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>1003701974</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>MORAN CABASCANGO TAMYA SISA</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>LICENCIADA MUSICA CONTEMPORANEA | TECNOLOGO EN DOCENCIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION INTERCULTURAL E INCLUSIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>0801572702</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>MOSQUERA  JARAMILLO ROSA ELENA</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION MENCION PSICOLOGIA EDUCATIVA Y ORIENTACION</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION SUPERIOR Y EQUIDAD DE GENERO | ESPECIALISTA EN DISEÑO Y GESTION DE PROYECTOS EDUCATIVOS Y SOCIALES CON ENFOQUE DE GENERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>0104532858</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>NAULA CHACA JUAN PABLO</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS | MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>1715952246</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>NEGRETE SALAZAR PABLO MARTIN</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>1707622112</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>NORIEGA FERNANDEZ RAMIRO FABRICIO</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>LICENCE DE LITTERATURE GENERALE ET COMPAREE</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>DOCTEUR EN LITTERATURE GENERALE ET COMPAREE | DIPLOME D`ETUDES APPROFONDIES LITTERATURE GENERALE ET COMPAREE MENTION TRES BIEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>1721744041</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>NUÑEZ BAYAS MARIA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION MENCION PROFESORA PARVULARIA | TECNOLOGO/A SUPERIOR EN ACTUACION Y DIRECCION ESCENICA</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA EN LAS ARTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>1719319665</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>NUÑEZ  MORETA MARIA JOSE</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION MENCION MUSICA LENGUAJE Y MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN GESTION Y EMPRENDIMIENTO DE PROYECTOS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>1716116023</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>OLEAS RUEDA MARIA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>SOCIOLOGA CON MENCION EN DESARROLLO</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>DOCTOR/A EN HISTORIA DE LOS ANDES | MAGISTER EN ESTUDIOS DE LA CULTURA MENCION ARTES Y ESTUDIOS VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>1002940599</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>OÑA FONSECA FRANCISCO JAVIER</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CINE Y AUDIOVISUALES | TECNOLOGO EN REALIZACION Y ACTUACION DE CINE</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DIRECCION Y DRAMATURGIAS CONTEMPORANEAS | MASTER UNIVERSITARIO EN DIRECCION DE MARKETING INTERNACIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>0915800478</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>ORTEGA HUERTA FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>ABOGADO DE LOS TRIBUNALES Y JUZGADOS DE LA REPUBLICA | BACHELOR OF MUSIC</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>1711603850</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>PALYS REYES ANA MARIA</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>PROFESORA DE EDUCACION MEDIA EN LA ESPECIALIDAD DE LENGUA Y LITERATURA | LICENCIADA EN CIENCIAS DE LA EDUCACION EN LA ESPECIALIDAD DE LENGUA Y LITERATURA</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION ARTES Y ESTUDIOS VISUALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>0502464282</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>PANCHI CULQUI JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION EDUCACION MUSICAL</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF MUSIC, CONTRABASS | MASTER OF MUSIC, MUSIC EDUCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>1003588488</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>PEÑAFIEL SOLANO CAMPO ELIAS</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN ARTES MUSICALES Y SONORAS | TECNOLOGO EN MUSICA MENCION PIANO</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN PEDAGOGIA MENCIÓN EN MUSICA Y DIRECCION CORAL | MAGISTER EN PEDAGOGIA MENCIÓN EN EDUCACION TECNICA Y TECNOLOGICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>1710294891</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>PEREZ ESCALANTE MYRIAN GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA CERAMICA</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>1710563220</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>PEREZ CONSUELO DEL ROCIO</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN CIENCIAS DE LA EDUCACION PROFESORA DE ENSEÑANZA MEDIA EN LA ESPECIALIZACION DE CASTELLANO Y LITERATURA</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DOCENCIA UNIVERSITARIA Y ADMINISTRACION EDUCATIVA | ESPECIALISTA EN DISEÑO CURRICULAR POR COMPETENCIAS | DOCTORA DENTRO DEL PROGRAMA DE DOCTORADO EN LENGUAS Y CULTURAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>0704360858</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>PESANTEZ CABRERA CARLOS BENITO</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>SOCIOLOGO</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN COMUNICACION CON MENCION EN OPINION PUBLICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>0801381294</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>PLAZA RODRIGUEZ GARY GASPAR</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>1709436123</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>PORTILLA KAROLIS CESAR AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>DOCTOR EN ESTETICA, CIENCIAS Y TECNOLOGIAS DE LAS ARTES - ESPECIALIDAD ARTES PLASTICAS Y FOTOGRAFIA | MASTER D´ARTS, MENTION ARTS PLASTIQUES, SPECIALITE THEORIE ET PRATIQUE DE L´ART CONTEMPORAIN E DES NOUVEAUX MEDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>1002015210</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>POZO RUIZ CARLOS EMILIO</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ESCULTURA GRABADO | TECNICO SUPERIOR EN ARTE GRAFICO</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>1713807020</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>PUEBLA CARDENAS OMAR DAVID</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES EN LAS ESPECIALIDADES DE ESCULTURA Y CERAMICA</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>1709162612</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>REVELO CARVAJAL CARLOS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>0151424520</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>RIOS LOPEZ JESUS</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>TITULO SUPERIOR DE MUSICA EN LA ESPECIALIDAD DE PIANO</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN FORMACION DEL PROFESORADO DE EDUCACION SECUNDARIA OBLIGATORIA Y BACHILLERATO, FORMACION PROFESIONAL Y ENSEÑANZA DE IDIOMAS EN LA ESPECIALIDAD EN MUSICA | MASTER ARTISTICO EN INTERPRETACION MUSICAL ESPECIALIDAD EN PIANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>1761226073</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>RIVERA CAMARGO GLORIA ESTEFANIA</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>MAESTRA EN MUSICA CON ENFASIS EN INTERPRETACION VIOLIN</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>MASTER EN ENSEÑANZAS ARTISTICAS EN INTERPRETACION DE MUSICA DE CAMARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>1758693855</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>RIVERO HERNANDEZ GILBERTO</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>1709635591</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PAZMINO LUIS DIMITROV</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN MUSICA | LICENCIADO EN MUSICA PERFIL COMPOSICION</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>1706950266</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PAZMIÑO ELENA PASIONARIA</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN HISTORIA DEL ARTE</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>LAUREA SPECIALISTICA IN STORIA DELL´ARTE MEDIEVALE, MODERNA E CONTEMPORANEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>1708241078</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ SANTAMARIA JUAN JOSE</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN COMUNICACION SOCIAL</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LITERATURA | MAGISTER EN ESTUDIOS DE LA CULTURA MENCION LITERATURA HISPANOAMERICANA | ESPECIALISTA SUPERIOR EN COMUNICACION MENCION COMUNICACION PARA LA EMPRESA | DOCTOR OF PHILOSOPHY IN LANGUAGES, CULTURES AND SOCIETIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>1710315993</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ  MERA SANTIAGO EDUARDO</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE ACTUACION</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>1711577070</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ROMERO NARVAEZ WILMER PATRICIO</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>1720761020</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>ROSERO MARIÑO NADIA CONSTANTINA</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>BACCALAUREUS ARTIUM LICENCIADO EN DISEÑO GRAFICO</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DRAMATURGIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>1711110930</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>ROSERO MOSCOSO MARIA SOL</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN GESTION PARA EL DESARROLLO LOCAL SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>MASTER ARTES MENCION DANZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>1719568303</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>RUIZ ANDRADE TAMIA MANAI</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF ARTS WITH A MAJOR IN THEATRE ARTS-DANCE</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF FINE ARTS IN DANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>1722501184</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>SALAS POLO BERNARDA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL | MASTER UNIVERSITARIO EN GESTION CULTURAL Y DE INDUSTRIAS CREATIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>1710285261</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ ARCOS VIVIANA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN GESTION PARA EL DESARROLLO LOCAL SOSTENIBLE | TECNOLOGO EN TERAPIAS NATURALES</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>1721238846</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ AUZ NATALY IVETH</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN ARTES MUSICALES CON ORIENTACION EN DIRECCION ORQUESTAL</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN INVESTIGACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>1716214315</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ BENAVIDES MAYRA DANIELA</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>DISEÑADORA CON MENCION EN DISEÑO DE PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF ARTS, PERFORMANCE DESIGN AND PRACTICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>1715543979</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>SANCHEZ ESPINOZA GILDA PAOLA</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN COMUNICACION SOCIAL | LICENCIADA EN ARTES, ESPECIALIZACION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA | MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>1714399100</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>SANTACRUZ VEGA LENNYN ARMANDO</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 2 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES MENCION ESCULTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ANTROPOLOGIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>1714724349</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>SANTANDER GUERRERO GABRIELA GLORIA</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES VISUALES</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LENGUAJES ARTISTICOS COMBINADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>1717124125</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS ARIAS CARLA MARIELA</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>BACHARELADO EM MUSICA COM HABILITACAO EM INSTRUMENTO</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>1710211465</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS AVILES NELSON ANIBAL</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE | DOCTOR DENTRO DEL PROGRAMA DE DOCTORADO EN ARTE: PRODUCCION E INVESTIGACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>0601901093</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS TEJADA CÉSAR AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSIATRIO EN EDUCACION UNIVERSITARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>1715745590</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>SOLORZANO  SANCHEZ CRISTINA ROCIO</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>PSICOLOGA</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>MAGÍSTER EN INNOVACIÓN DE LA EDUCACIÓN | ESPECIALISTA EN GESTION DE LA CALIDAD EN EDUCACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>1710438589</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>SUBIA VALDEZ JOSE RAFAEL</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN COMPOSICION CON MEDIOS ELECTROACUSTICOS</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>MASTER OF SCIENCE IN DIGITAL COMPOSITION AND PERFORMANCE | DOCTOR OF PHILOSOPHY IN MUSICAL COMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>1711742211</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>TAPIA CRUZ JHOFFRE WASHINGTON</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES MENCION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN DIRECCION Y DRAMATURGIAS CONTEMPORANEAS | MASTER UNIVERSITARIO EN ESTUDIOS AVANZADOS DE TEATRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>1755904800</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>TARAZONA VENTO BEATRIZ</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>0603584350</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>TAYUPANDA ASHQUI CESAR BENITO</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN CIENCIAS DE LA EDUCACION MENCION INSTRUMENTISTA PEDAGOGO EN CLARINETE</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN MUSICOLOGIA | MASTER UNIVERSITARIO EN PEDAGOGIA MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>DANZA (R)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>1713241279</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>TERAN ESPINOSA MARIA ENRIQUETA</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO/A EN DANZA</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>MASTER UNIVERSITARIO EN DOCENCIA UNIVERSITARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>1709984262</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>TITUAÑA LEMA MARTIN SAMUEL</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES MENCION ESCULTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION POLITICAS CULTURALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>1711257483</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>TORAL ZAVALA OMAR ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>PROFESOR DE MUSICA INSTRUMENTO PRINCIPAL GUITARRA</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN INTERPRETACION DE MUSICA LATINOAMERICANA DEL SIGLO XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>1712205325</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>TORRES GANGULA ANDRES SANTIAGO</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>No registra</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>TEACHER´S TRAINING SPECIALIZATION PIANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>0601809155</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>UNDA LARA SANTIAGO ULISES</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION DE PINTURA GRABADO</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA MENCION COMUNICACION | DOCTOR OF PHILOSOPHY IN VISUAL ARTS | MASTER OF FINE ARTS IN ELECTRONIC INTEGRATED ARTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>1757190648</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>URIBE SOTO RAFAEL ALONSO</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>INGENIERO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>DOCTOR EN CIENCIAS (QUIMICAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>1714158142</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>VACA TAMAYO EDISON ALVENIZ</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACIONES PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>1710020130</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>VALENCIA HINESTROSA JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ACTUACION TEATRAL | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>1707593594</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>VALLEJO ARISTIZABAL JOSE PATRICIO</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN SOCIOLOGIA Y CIENCIAS POLITICAS</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN LETRAS MENCION ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>1712170222</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>VARGAS VILLALBA MARIO FIDEL</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO MUSICA CONTEMPORANEA</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN EDUCACION MUSICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1712193620</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>VELA MOSQUERA ANDREA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>BACHELOR OF MUSIC IN PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN LA ESPECIALIDAD DE DIRECCION DE ORQUESTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>1705863049</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>VERDESOTO JACOME IRINA MARIBEL</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 NOMBRAMIENTO MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADA EN ARTES MENCION ACTUACION</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN CIENCIAS SOCIALES CON MENCION EN ANTROPOLOGIA | DIPLOMA SUPERIOR EN ARTES ESCENICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ARTES ESCENICAS (R)</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>1712410172</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>VILLACIS GUERRERO OMAR STALIN</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO PARCIAL </t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ACTUACION TEATRAL</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DE LA CULTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>1715000608</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>VITERI  CHAVEZ CHRISTIAN PATRICIO</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGADO 3 NOMBRAMIENTO TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN ARTES ESPECIALIZACIONES PINTURA Y GRABADO</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN ESTUDIOS DEL ARTE | ESPECIALISTA EN ESTUDIOS DEL ARTE | DIPLOMA SUPERIOR EN ESTUDIOS DEL ARTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>ARTES PLASTICAS (R)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>1715706238</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>ZALDUMBIDE MANOSALVAS JORGE LUIS</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA TIEMPO COMPLETO </t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>INGENIERO EN DISEÑO GRAFICO EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN LENGUAJES ARTISTICOS COMBINADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ARTES</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ARTES MUSICALES (R)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>0201860731</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>ZAPATA ESQUIVEL ALEXIS DAVID</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUXILIAR 1 CONTRATO CON RELACION DE DEPENDENCIA MEDIO TIEMPO </t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>LICENCIADO EN MUSICA</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>MAGISTER EN INNOVACION EN EDUCACION | MASTER UNIVERSITARIO EN COMPOSICION MUSICAL CON NUEVAS TECNOLOGIAS</t>
         </is>
       </c>
     </row>

--- a/outputs/matriz_procesada.xlsx
+++ b/outputs/matriz_procesada.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:ZZ5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,11 @@
         </is>
       </c>
       <c r="F1" s="4" t="n"/>
+      <c r="ZZ1" t="inlineStr">
+        <is>
+          <t>Trigger: 1786133639.465325</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="C2" s="4" t="inlineStr">

--- a/outputs/matriz_procesada.xlsx
+++ b/outputs/matriz_procesada.xlsx
@@ -514,7 +514,7 @@
       <c r="F1" s="4" t="n"/>
       <c r="ZZ1" t="inlineStr">
         <is>
-          <t>Trigger: 1786133639.465325</t>
+          <t>Trigger: 1786135065.3799152</t>
         </is>
       </c>
     </row>
